--- a/docs/downloads/20261008_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20261008_Johor_Teduh_Weekly_Update.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BB21"/>
+  <dimension ref="A2:BE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,10 @@
     <col width="9" customWidth="1" min="51" max="51"/>
     <col width="9" customWidth="1" min="52" max="52"/>
     <col width="9" customWidth="1" min="53" max="53"/>
-    <col width="46" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="54" max="54"/>
+    <col width="9" customWidth="1" min="55" max="55"/>
+    <col width="9" customWidth="1" min="56" max="56"/>
+    <col width="46" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -611,8 +614,11 @@
       <c r="AV3" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="AY3" s="4" t="n">
+      <c r="AY3" s="3" t="n">
         <v>46297</v>
+      </c>
+      <c r="BB3" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -868,22 +874,37 @@
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="AY4" s="6" t="inlineStr">
+      <c r="AY4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AZ4" s="6" t="inlineStr">
+      <c r="AZ4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BA4" s="6" t="inlineStr">
+      <c r="BA4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="BB4" s="5" t="inlineStr">
+      <c r="BB4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="BC4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BD4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="BE4" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
@@ -948,6 +969,9 @@
       <c r="AZ5" s="8" t="n"/>
       <c r="BA5" s="8" t="n"/>
       <c r="BB5" s="8" t="n"/>
+      <c r="BC5" s="8" t="n"/>
+      <c r="BD5" s="8" t="n"/>
+      <c r="BE5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1131,20 +1155,31 @@
         <f>AW6/$D$6</f>
         <v/>
       </c>
-      <c r="AY6" s="14">
+      <c r="AY6" s="12">
         <f>AZ6-AW6</f>
         <v/>
       </c>
-      <c r="AZ6" s="14" t="n">
+      <c r="AZ6" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="BA6" s="15">
+      <c r="BA6" s="13">
         <f>AZ6/$D$6</f>
         <v/>
       </c>
-      <c r="BB6" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 196 units, Block B: 132 units</t>
+      <c r="BB6" s="14">
+        <f>BC6-AZ6</f>
+        <v/>
+      </c>
+      <c r="BC6" s="14" t="n">
+        <v>335</v>
+      </c>
+      <c r="BD6" s="15">
+        <f>BC6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BE6" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 197 units, Block B: 138 units</t>
         </is>
       </c>
     </row>
@@ -1330,20 +1365,31 @@
         <f>AW7/$D$7</f>
         <v/>
       </c>
-      <c r="AY7" s="14">
+      <c r="AY7" s="12">
         <f>AZ7-AW7</f>
         <v/>
       </c>
-      <c r="AZ7" s="14" t="n">
+      <c r="AZ7" s="12" t="n">
         <v>1017</v>
       </c>
-      <c r="BA7" s="15">
+      <c r="BA7" s="13">
         <f>AZ7/$D$7</f>
         <v/>
       </c>
-      <c r="BB7" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 417 units, Block B: 394 units, Block C: 92 units, Block D: 114 units</t>
+      <c r="BB7" s="14">
+        <f>BC7-AZ7</f>
+        <v/>
+      </c>
+      <c r="BC7" s="14" t="n">
+        <v>1025</v>
+      </c>
+      <c r="BD7" s="15">
+        <f>BC7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BE7" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 422 units, Block B: 397 units, Block C: 92 units, Block D: 114 units</t>
         </is>
       </c>
     </row>
@@ -1529,18 +1575,29 @@
         <f>AW8/$D$8</f>
         <v/>
       </c>
-      <c r="AY8" s="14">
+      <c r="AY8" s="12">
         <f>AZ8-AW8</f>
         <v/>
       </c>
-      <c r="AZ8" s="14" t="n">
+      <c r="AZ8" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="BA8" s="15">
+      <c r="BA8" s="13">
         <f>AZ8/$D$8</f>
         <v/>
       </c>
-      <c r="BB8" s="10" t="inlineStr">
+      <c r="BB8" s="14">
+        <f>BC8-AZ8</f>
+        <v/>
+      </c>
+      <c r="BC8" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD8" s="15">
+        <f>BC8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BE8" s="10" t="inlineStr">
         <is>
           <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
@@ -1728,20 +1785,31 @@
         <f>AW9/$D$9</f>
         <v/>
       </c>
-      <c r="AY9" s="14">
+      <c r="AY9" s="12">
         <f>AZ9-AW9</f>
         <v/>
       </c>
-      <c r="AZ9" s="14" t="n">
+      <c r="AZ9" s="12" t="n">
         <v>1091</v>
       </c>
-      <c r="BA9" s="15">
+      <c r="BA9" s="13">
         <f>AZ9/$D$9</f>
         <v/>
       </c>
-      <c r="BB9" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Phase 1: 671 units, Phase 2: 420 units</t>
+      <c r="BB9" s="14">
+        <f>BC9-AZ9</f>
+        <v/>
+      </c>
+      <c r="BC9" s="14" t="n">
+        <v>1096</v>
+      </c>
+      <c r="BD9" s="15">
+        <f>BC9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BE9" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Phase 1: 671 units, Phase 2: 425 units</t>
         </is>
       </c>
     </row>
@@ -1804,6 +1872,9 @@
       <c r="AZ10" s="8" t="n"/>
       <c r="BA10" s="8" t="n"/>
       <c r="BB10" s="8" t="n"/>
+      <c r="BC10" s="8" t="n"/>
+      <c r="BD10" s="8" t="n"/>
+      <c r="BE10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1987,18 +2058,29 @@
         <f>AW11/$D$11</f>
         <v/>
       </c>
-      <c r="AY11" s="14">
+      <c r="AY11" s="12">
         <f>AZ11-AW11</f>
         <v/>
       </c>
-      <c r="AZ11" s="14" t="n">
+      <c r="AZ11" s="12" t="n">
         <v>844</v>
       </c>
-      <c r="BA11" s="15">
+      <c r="BA11" s="13">
         <f>AZ11/$D$11</f>
         <v/>
       </c>
-      <c r="BB11" s="10" t="inlineStr">
+      <c r="BB11" s="14">
+        <f>BC11-AZ11</f>
+        <v/>
+      </c>
+      <c r="BC11" s="14" t="n">
+        <v>845</v>
+      </c>
+      <c r="BD11" s="15">
+        <f>BC11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BE11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2186,20 +2268,31 @@
         <f>AW12/$D$12</f>
         <v/>
       </c>
-      <c r="AY12" s="14">
+      <c r="AY12" s="12">
         <f>AZ12-AW12</f>
         <v/>
       </c>
-      <c r="AZ12" s="14" t="n">
+      <c r="AZ12" s="12" t="n">
         <v>1569</v>
       </c>
-      <c r="BA12" s="15">
+      <c r="BA12" s="13">
         <f>AZ12/$D$12</f>
         <v/>
       </c>
-      <c r="BB12" s="10" t="inlineStr">
-        <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 533 units, Block B: 541 units, Block D: 495 units</t>
+      <c r="BB12" s="14">
+        <f>BC12-AZ12</f>
+        <v/>
+      </c>
+      <c r="BC12" s="14" t="n">
+        <v>1581</v>
+      </c>
+      <c r="BD12" s="15">
+        <f>BC12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BE12" s="10" t="inlineStr">
+        <is>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 538 units, Block B: 546 units, Block D: 497 units</t>
         </is>
       </c>
     </row>
@@ -2385,20 +2478,31 @@
         <f>AW13/$D$13</f>
         <v/>
       </c>
-      <c r="AY13" s="14">
+      <c r="AY13" s="12">
         <f>AZ13-AW13</f>
         <v/>
       </c>
-      <c r="AZ13" s="14" t="n">
+      <c r="AZ13" s="12" t="n">
         <v>1064</v>
       </c>
-      <c r="BA13" s="15">
+      <c r="BA13" s="13">
         <f>AZ13/$D$13</f>
         <v/>
       </c>
-      <c r="BB13" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 412 units, Block B: 384 units, Block C: 268 units</t>
+      <c r="BB13" s="14">
+        <f>BC13-AZ13</f>
+        <v/>
+      </c>
+      <c r="BC13" s="14" t="n">
+        <v>1074</v>
+      </c>
+      <c r="BD13" s="15">
+        <f>BC13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BE13" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 414 units, Block B: 388 units, Block C: 272 units</t>
         </is>
       </c>
     </row>
@@ -2584,20 +2688,31 @@
         <f>AW14/$D$14</f>
         <v/>
       </c>
-      <c r="AY14" s="14">
+      <c r="AY14" s="12">
         <f>AZ14-AW14</f>
         <v/>
       </c>
-      <c r="AZ14" s="14" t="n">
+      <c r="AZ14" s="12" t="n">
         <v>813</v>
       </c>
-      <c r="BA14" s="15">
+      <c r="BA14" s="13">
         <f>AZ14/$D$14</f>
         <v/>
       </c>
-      <c r="BB14" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 526 units, Block B: 287 units</t>
+      <c r="BB14" s="14">
+        <f>BC14-AZ14</f>
+        <v/>
+      </c>
+      <c r="BC14" s="14" t="n">
+        <v>831</v>
+      </c>
+      <c r="BD14" s="15">
+        <f>BC14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BE14" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 533 units, Block B: 298 units</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2898,31 @@
         <f>AW15/$D$15</f>
         <v/>
       </c>
-      <c r="AY15" s="14">
+      <c r="AY15" s="12">
         <f>AZ15-AW15</f>
         <v/>
       </c>
-      <c r="AZ15" s="14" t="n">
+      <c r="AZ15" s="12" t="n">
         <v>1415</v>
       </c>
-      <c r="BA15" s="15">
+      <c r="BA15" s="13">
         <f>AZ15/$D$15</f>
         <v/>
       </c>
-      <c r="BB15" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 732 units, Block B: 683 units</t>
+      <c r="BB15" s="14">
+        <f>BC15-AZ15</f>
+        <v/>
+      </c>
+      <c r="BC15" s="14" t="n">
+        <v>1419</v>
+      </c>
+      <c r="BD15" s="15">
+        <f>BC15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BE15" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 734 units, Block B: 685 units</t>
         </is>
       </c>
     </row>
@@ -2982,18 +3108,29 @@
         <f>AW16/$D$16</f>
         <v/>
       </c>
-      <c r="AY16" s="14">
+      <c r="AY16" s="12">
         <f>AZ16-AW16</f>
         <v/>
       </c>
-      <c r="AZ16" s="14" t="n">
+      <c r="AZ16" s="12" t="n">
         <v>922</v>
       </c>
-      <c r="BA16" s="15">
+      <c r="BA16" s="13">
         <f>AZ16/$D$16</f>
         <v/>
       </c>
-      <c r="BB16" s="10" t="inlineStr">
+      <c r="BB16" s="14">
+        <f>BC16-AZ16</f>
+        <v/>
+      </c>
+      <c r="BC16" s="14" t="n">
+        <v>924</v>
+      </c>
+      <c r="BD16" s="15">
+        <f>BC16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BE16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3123,10 +3260,13 @@
       <c r="AV17" s="12" t="n"/>
       <c r="AW17" s="12" t="n"/>
       <c r="AX17" s="13" t="n"/>
-      <c r="AY17" s="14" t="n"/>
-      <c r="AZ17" s="14" t="n"/>
-      <c r="BA17" s="15" t="n"/>
-      <c r="BB17" s="10" t="inlineStr">
+      <c r="AY17" s="12" t="n"/>
+      <c r="AZ17" s="12" t="n"/>
+      <c r="BA17" s="13" t="n"/>
+      <c r="BB17" s="14" t="n"/>
+      <c r="BC17" s="14" t="n"/>
+      <c r="BD17" s="15" t="n"/>
+      <c r="BE17" s="10" t="inlineStr">
         <is>
           <t>*No info on Teduh, Not obtained AP.</t>
         </is>
@@ -3314,20 +3454,31 @@
         <f>AW18/$D$18</f>
         <v/>
       </c>
-      <c r="AY18" s="14">
+      <c r="AY18" s="12">
         <f>AZ18-AW18</f>
         <v/>
       </c>
-      <c r="AZ18" s="14" t="n">
+      <c r="AZ18" s="12" t="n">
         <v>745</v>
       </c>
-      <c r="BA18" s="15">
+      <c r="BA18" s="13">
         <f>AZ18/$D$18</f>
         <v/>
       </c>
-      <c r="BB18" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 455 units, Block B: 290 units</t>
+      <c r="BB18" s="14">
+        <f>BC18-AZ18</f>
+        <v/>
+      </c>
+      <c r="BC18" s="14" t="n">
+        <v>749</v>
+      </c>
+      <c r="BD18" s="15">
+        <f>BC18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BE18" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 457 units, Block B: 292 units</t>
         </is>
       </c>
     </row>
@@ -3513,20 +3664,31 @@
         <f>AW19/$D$19</f>
         <v/>
       </c>
-      <c r="AY19" s="14">
+      <c r="AY19" s="12">
         <f>AZ19-AW19</f>
         <v/>
       </c>
-      <c r="AZ19" s="14" t="n">
+      <c r="AZ19" s="12" t="n">
         <v>407</v>
       </c>
-      <c r="BA19" s="15">
+      <c r="BA19" s="13">
         <f>AZ19/$D$19</f>
         <v/>
       </c>
-      <c r="BB19" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 301 units, Block B: 106 units</t>
+      <c r="BB19" s="14">
+        <f>BC19-AZ19</f>
+        <v/>
+      </c>
+      <c r="BC19" s="14" t="n">
+        <v>409</v>
+      </c>
+      <c r="BD19" s="15">
+        <f>BC19/$D$19</f>
+        <v/>
+      </c>
+      <c r="BE19" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 302 units, Block B: 107 units</t>
         </is>
       </c>
     </row>
@@ -3712,20 +3874,31 @@
         <f>AW20/$D$20</f>
         <v/>
       </c>
-      <c r="AY20" s="14">
+      <c r="AY20" s="12">
         <f>AZ20-AW20</f>
         <v/>
       </c>
-      <c r="AZ20" s="14" t="n">
+      <c r="AZ20" s="12" t="n">
         <v>333</v>
       </c>
-      <c r="BA20" s="15">
+      <c r="BA20" s="13">
         <f>AZ20/$D$20</f>
         <v/>
       </c>
-      <c r="BB20" s="10" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 227 units, Block B: 106 units</t>
+      <c r="BB20" s="14">
+        <f>BC20-AZ20</f>
+        <v/>
+      </c>
+      <c r="BC20" s="14" t="n">
+        <v>341</v>
+      </c>
+      <c r="BD20" s="15">
+        <f>BC20/$D$20</f>
+        <v/>
+      </c>
+      <c r="BE20" s="10" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 229 units, Block B: 112 units</t>
         </is>
       </c>
     </row>
@@ -3815,22 +3988,34 @@
         <f>AW21/$D$21</f>
         <v/>
       </c>
-      <c r="AY21" s="14">
+      <c r="AY21" s="12">
         <f>AZ21-AW21</f>
         <v/>
       </c>
-      <c r="AZ21" s="14" t="n">
+      <c r="AZ21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="BA21" s="15">
+      <c r="BA21" s="13">
         <f>AZ21/$D$21</f>
         <v/>
       </c>
-      <c r="BB21" s="10" t="inlineStr"/>
+      <c r="BB21" s="14">
+        <f>BC21-AZ21</f>
+        <v/>
+      </c>
+      <c r="BC21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="15">
+        <f>BC21/$D$21</f>
+        <v/>
+      </c>
+      <c r="BE21" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="R3:T3"/>
     <mergeCell ref="U3:W3"/>
     <mergeCell ref="AD3:AF3"/>
